--- a/backend/data/uploads/EES/JIG_관리대장.xlsx
+++ b/backend/data/uploads/EES/JIG_관리대장.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\EES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23697561-0DC7-4801-AFA4-8B35A93DCCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0D59A42-DC29-4528-96E3-85AEB4DED56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="5" xr2:uid="{0BC09096-1F1E-4936-BA95-0C97FA46254D}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="6" xr2:uid="{4325647D-0B5B-49BB-B908-B59607F1C48E}"/>
   </bookViews>
   <sheets>
     <sheet name="음극 Notching 금형" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="상면 Forming 금형" sheetId="4" r:id="rId4"/>
     <sheet name="하면 Forming 금형" sheetId="5" r:id="rId5"/>
     <sheet name="음극 Stack 금형" sheetId="6" r:id="rId6"/>
+    <sheet name="미등록 Notching 금형" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="43">
   <si>
     <t>이벤트시간</t>
   </si>
@@ -153,6 +154,12 @@
   </si>
   <si>
     <t>Pouch #2(L)</t>
+  </si>
+  <si>
+    <t>POU WND99_Unknown_01</t>
+  </si>
+  <si>
+    <t>Pouch #99(S)</t>
   </si>
 </sst>
 </file>
@@ -533,7 +540,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A3A22A-7D00-441F-895F-EA23D1C29D44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247E8AC3-D5F0-4630-A317-9BFA7087291D}">
   <dimension ref="B2:X6"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -724,7 +731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA3A1B-6C37-44A3-8E24-DC1783770A75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3FFAD3F-0BCE-4A12-B184-86E77A6E841E}">
   <dimension ref="B2:X8"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -961,7 +968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C94B995-0394-4496-A82B-C8357FA52864}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{557A3197-55E3-42A4-B1DD-E15EA02774FB}">
   <dimension ref="B2:X6"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1152,7 +1159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE58EABD-AA0C-4064-8165-BA2D236AADB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3FA398-24C9-4BAF-9438-A9BD0E68186E}">
   <dimension ref="B2:X6"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1343,7 +1350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BAB55A-5DB4-4FFE-864E-4AA718823420}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2F0152-D2FD-4AFF-A791-B8A193C22244}">
   <dimension ref="B2:X5"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1511,7 +1518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F075346C-B895-4567-A6B4-30C7B38EBFCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7931026F-2645-4668-97CE-19DC781487A8}">
   <dimension ref="B2:X6"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -1699,4 +1706,195 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F483799-73D7-4890-AA8E-977EA3ED793A}">
+  <dimension ref="B2:X6"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.78515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.2109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.35546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="10.35546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="9.2109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.78515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="2">
+        <v>46195.325694444444</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="2">
+        <v>46195.333333333336</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="2">
+        <v>46209.333333333336</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="2">
+        <v>46210.333333333336</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/backend/data/uploads/EES/JIG_관리대장.xlsx
+++ b/backend/data/uploads/EES/JIG_관리대장.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\EES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0D59A42-DC29-4528-96E3-85AEB4DED56C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{187853D2-6BB5-4210-B619-EEFA33FA314F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="6" xr2:uid="{4325647D-0B5B-49BB-B908-B59607F1C48E}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="6" xr2:uid="{B4DF089E-418F-4668-9178-3B855912B1DF}"/>
   </bookViews>
   <sheets>
-    <sheet name="음극 Notching 금형" sheetId="1" r:id="rId1"/>
-    <sheet name="양극 Notching 금형" sheetId="2" r:id="rId2"/>
-    <sheet name="음극 Cutting 금형" sheetId="3" r:id="rId3"/>
-    <sheet name="상면 Forming 금형" sheetId="4" r:id="rId4"/>
-    <sheet name="하면 Forming 금형" sheetId="5" r:id="rId5"/>
-    <sheet name="음극 Stack 금형" sheetId="6" r:id="rId6"/>
-    <sheet name="미등록 Notching 금형" sheetId="7" r:id="rId7"/>
+    <sheet name="#RX39513" sheetId="1" r:id="rId1"/>
+    <sheet name="#RX28312" sheetId="2" r:id="rId2"/>
+    <sheet name="#RX28315" sheetId="3" r:id="rId3"/>
+    <sheet name="#RX50177" sheetId="4" r:id="rId4"/>
+    <sheet name="#RX41194" sheetId="5" r:id="rId5"/>
+    <sheet name="#RX39002" sheetId="6" r:id="rId6"/>
+    <sheet name="#RX77777" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="46">
   <si>
     <t>이벤트시간</t>
   </si>
@@ -129,12 +129,18 @@
     <t>내부 수리</t>
   </si>
   <si>
+    <t>사용 대기 보관함</t>
+  </si>
+  <si>
+    <t>외부 수리</t>
+  </si>
+  <si>
+    <t>반납 대기 보관함</t>
+  </si>
+  <si>
     <t>POU WND10_Stack(1차)_02</t>
   </si>
   <si>
-    <t>사용 대기 보관함</t>
-  </si>
-  <si>
     <t>POU WND11_Stack(1차)_01</t>
   </si>
   <si>
@@ -154,6 +160,9 @@
   </si>
   <si>
     <t>Pouch #2(L)</t>
+  </si>
+  <si>
+    <t>폐기</t>
   </si>
   <si>
     <t>POU WND99_Unknown_01</t>
@@ -540,8 +549,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247E8AC3-D5F0-4630-A317-9BFA7087291D}">
-  <dimension ref="B2:X6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2755DB6-658D-4C57-84E0-84ED6F9F448B}">
+  <dimension ref="B2:X14"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -634,7 +643,7 @@
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2">
-        <v>46190.28402777778</v>
+        <v>46190.333333333336</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -657,7 +666,7 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2">
-        <v>46190.291666666664</v>
+        <v>46190.333333333336</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
@@ -721,6 +730,190 @@
         <v>27</v>
       </c>
       <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="2">
+        <v>46208.625</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="2">
+        <v>46209.375</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="2">
+        <v>46209.875</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="2">
+        <v>46212.333333333336</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="2">
+        <v>46213.333333333336</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2">
+        <v>46215.416666666664</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="2">
+        <v>46218.25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="2">
+        <v>46218.75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" t="s">
         <v>28</v>
       </c>
     </row>
@@ -731,8 +924,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3FFAD3F-0BCE-4A12-B184-86E77A6E841E}">
-  <dimension ref="B2:X8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCFD5505-F27B-476D-A3CF-CC44D12C23FB}">
+  <dimension ref="B2:X13"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -825,13 +1018,13 @@
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2">
-        <v>46191.34652777778</v>
+        <v>46191.375</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -848,13 +1041,13 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2">
-        <v>46191.354166666664</v>
+        <v>46191.375</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -871,13 +1064,13 @@
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="2">
-        <v>46205.354166666664</v>
+        <v>46205.333333333336</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -897,10 +1090,10 @@
         <v>46206.375</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
         <v>25</v>
@@ -917,13 +1110,13 @@
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="2">
-        <v>46214.25</v>
+        <v>46207.375</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>25</v>
@@ -940,13 +1133,13 @@
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="2">
-        <v>46214.833333333336</v>
+        <v>46209.583333333336</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
         <v>25</v>
@@ -958,6 +1151,121 @@
         <v>27</v>
       </c>
       <c r="K8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="2">
+        <v>46211.291666666664</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="2">
+        <v>46211.791666666664</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="2">
+        <v>46214.25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2">
+        <v>46214.833333333336</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="2">
+        <v>46216.375</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" t="s">
         <v>28</v>
       </c>
     </row>
@@ -968,8 +1276,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{557A3197-55E3-42A4-B1DD-E15EA02774FB}">
-  <dimension ref="B2:X6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBAA5DA-9EDE-4F51-A86E-A77555913A4B}">
+  <dimension ref="B2:X13"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1062,13 +1370,13 @@
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2">
-        <v>46197.242361111108</v>
+        <v>46193.416666666664</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -1077,7 +1385,7 @@
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
@@ -1085,13 +1393,13 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2">
-        <v>46197.25</v>
+        <v>46193.416666666664</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -1100,7 +1408,7 @@
         <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K4" t="s">
         <v>28</v>
@@ -1114,7 +1422,7 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -1123,7 +1431,7 @@
         <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K5" t="s">
         <v>28</v>
@@ -1137,7 +1445,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
         <v>25</v>
@@ -1146,9 +1454,170 @@
         <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="2">
+        <v>46212.333333333336</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="2">
+        <v>46212.583333333336</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="2">
+        <v>46213.083333333336</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="2">
+        <v>46214.375</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="2">
+        <v>46216.458333333336</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2">
+        <v>46217.25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="2">
+        <v>46219.25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1159,8 +1628,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3FA398-24C9-4BAF-9438-A9BD0E68186E}">
-  <dimension ref="B2:X6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F79E14D4-91D1-44EA-968F-598670DA2FAD}">
+  <dimension ref="B2:X13"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1253,13 +1722,13 @@
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2">
-        <v>46199.90902777778</v>
+        <v>46195.333333333336</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -1268,7 +1737,7 @@
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
@@ -1276,13 +1745,13 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2">
-        <v>46199.916666666664</v>
+        <v>46195.333333333336</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -1291,7 +1760,7 @@
         <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
         <v>28</v>
@@ -1305,7 +1774,7 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -1314,7 +1783,7 @@
         <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
         <v>28</v>
@@ -1325,21 +1794,182 @@
         <v>46215.125</v>
       </c>
       <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="2">
+        <v>46216.958333333336</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="2">
+        <v>46217.125</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="2">
+        <v>46219.875</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="2">
+        <v>46220.833333333336</v>
+      </c>
+      <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="2">
+        <v>46221.416666666664</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2">
+        <v>46222.916666666664</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="2">
+        <v>46223.958333333336</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1350,8 +1980,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2F0152-D2FD-4AFF-A791-B8A193C22244}">
-  <dimension ref="B2:X5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932457E-04DE-450A-A40E-064B2E3FF52C}">
+  <dimension ref="B2:X13"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1444,13 +2074,13 @@
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2">
-        <v>46203.367361111108</v>
+        <v>46198.375</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -1459,7 +2089,7 @@
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
@@ -1467,13 +2097,13 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2">
-        <v>46203.375</v>
+        <v>46198.375</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -1482,7 +2112,7 @@
         <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
         <v>28</v>
@@ -1490,13 +2120,13 @@
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="2">
-        <v>46217.375</v>
+        <v>46208.333333333336</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -1505,9 +2135,193 @@
         <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="2">
+        <v>46209.333333333336</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="2">
+        <v>46210.416666666664</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="2">
+        <v>46212.291666666664</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="2">
+        <v>46212.791666666664</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="2">
+        <v>46214.333333333336</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="2">
+        <v>46215.333333333336</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2">
+        <v>46216.375</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="2">
+        <v>46217.375</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1518,8 +2332,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7931026F-2645-4668-97CE-19DC781487A8}">
-  <dimension ref="B2:X6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A975AA48-4E30-44C1-B066-D80098E7BD9D}">
+  <dimension ref="B2:X12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1612,13 +2426,13 @@
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2">
-        <v>46205.28402777778</v>
+        <v>46201.333333333336</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -1627,7 +2441,7 @@
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
@@ -1635,13 +2449,13 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2">
-        <v>46205.291666666664</v>
+        <v>46201.333333333336</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -1650,7 +2464,7 @@
         <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
         <v>28</v>
@@ -1664,7 +2478,7 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -1673,7 +2487,7 @@
         <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
         <v>28</v>
@@ -1687,7 +2501,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
         <v>25</v>
@@ -1696,9 +2510,147 @@
         <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="2">
+        <v>46223.625</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="2">
+        <v>46224.375</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="2">
+        <v>46225.25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="2">
+        <v>46225.75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="2">
+        <v>46226.375</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2">
+        <v>46227.416666666664</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1709,8 +2661,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F483799-73D7-4890-AA8E-977EA3ED793A}">
-  <dimension ref="B2:X6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5C906C0-FF74-427B-9DD6-094006EFA96E}">
+  <dimension ref="B2:X12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1803,13 +2755,13 @@
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2">
-        <v>46195.325694444444</v>
+        <v>46203.333333333336</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
         <v>25</v>
@@ -1818,7 +2770,7 @@
         <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K3" t="s">
         <v>28</v>
@@ -1826,13 +2778,13 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2">
-        <v>46195.333333333336</v>
+        <v>46203.333333333336</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H4" t="s">
         <v>25</v>
@@ -1841,7 +2793,7 @@
         <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
         <v>28</v>
@@ -1855,7 +2807,7 @@
         <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -1864,7 +2816,7 @@
         <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K5" t="s">
         <v>28</v>
@@ -1878,7 +2830,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
         <v>25</v>
@@ -1887,9 +2839,147 @@
         <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="2">
+        <v>46211.416666666664</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="2">
+        <v>46212.25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="2">
+        <v>46212.75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="2">
+        <v>46214.291666666664</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="2">
+        <v>46215.291666666664</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="2">
+        <v>46216.375</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" t="s">
         <v>28</v>
       </c>
     </row>
